--- a/Дело3а-78-2026Таганай/12_Разнарядки/Разнорядки 2025/Сводная_ведомость.xlsx
+++ b/Дело3а-78-2026Таганай/12_Разнарядки/Разнорядки 2025/Сводная_ведомость.xlsx
@@ -651,7 +651,7 @@
         </is>
       </c>
       <c r="I6" s="7" t="n">
-        <v>46157.9254412663</v>
+        <v>46157.93119981579</v>
       </c>
     </row>
     <row r="7" ht="15" customHeight="1">

--- a/Дело3а-78-2026Таганай/12_Разнарядки/Разнорядки 2025/Сводная_ведомость.xlsx
+++ b/Дело3а-78-2026Таганай/12_Разнарядки/Разнорядки 2025/Сводная_ведомость.xlsx
@@ -651,7 +651,7 @@
         </is>
       </c>
       <c r="I6" s="7" t="n">
-        <v>46157.93119981579</v>
+        <v>46157.93371403145</v>
       </c>
     </row>
     <row r="7" ht="15" customHeight="1">

--- a/Дело3а-78-2026Таганай/12_Разнарядки/Разнорядки 2025/Сводная_ведомость.xlsx
+++ b/Дело3а-78-2026Таганай/12_Разнарядки/Разнорядки 2025/Сводная_ведомость.xlsx
@@ -651,7 +651,7 @@
         </is>
       </c>
       <c r="I6" s="7" t="n">
-        <v>46157.93371403145</v>
+        <v>46157.93678029199</v>
       </c>
     </row>
     <row r="7" ht="15" customHeight="1">

--- a/Дело3а-78-2026Таганай/12_Разнарядки/Разнорядки 2025/Сводная_ведомость.xlsx
+++ b/Дело3а-78-2026Таганай/12_Разнарядки/Разнорядки 2025/Сводная_ведомость.xlsx
@@ -651,7 +651,7 @@
         </is>
       </c>
       <c r="I6" s="7" t="n">
-        <v>46157.93678029199</v>
+        <v>46158.28197430164</v>
       </c>
     </row>
     <row r="7" ht="15" customHeight="1">

--- a/Дело3а-78-2026Таганай/12_Разнарядки/Разнорядки 2025/Сводная_ведомость.xlsx
+++ b/Дело3а-78-2026Таганай/12_Разнарядки/Разнорядки 2025/Сводная_ведомость.xlsx
@@ -651,7 +651,7 @@
         </is>
       </c>
       <c r="I6" s="7" t="n">
-        <v>46158.28197430164</v>
+        <v>46158.29723315082</v>
       </c>
     </row>
     <row r="7" ht="15" customHeight="1">

--- a/Дело3а-78-2026Таганай/12_Разнарядки/Разнорядки 2025/Сводная_ведомость.xlsx
+++ b/Дело3а-78-2026Таганай/12_Разнарядки/Разнорядки 2025/Сводная_ведомость.xlsx
@@ -651,7 +651,7 @@
         </is>
       </c>
       <c r="I6" s="7" t="n">
-        <v>46158.29723315082</v>
+        <v>46158.29794191419</v>
       </c>
     </row>
     <row r="7" ht="15" customHeight="1">

--- a/Дело3а-78-2026Таганай/12_Разнарядки/Разнорядки 2025/Сводная_ведомость.xlsx
+++ b/Дело3а-78-2026Таганай/12_Разнарядки/Разнорядки 2025/Сводная_ведомость.xlsx
@@ -651,7 +651,7 @@
         </is>
       </c>
       <c r="I6" s="7" t="n">
-        <v>46158.29794191419</v>
+        <v>46158.33358836502</v>
       </c>
     </row>
     <row r="7" ht="15" customHeight="1">

--- a/Дело3а-78-2026Таганай/12_Разнарядки/Разнорядки 2025/Сводная_ведомость.xlsx
+++ b/Дело3а-78-2026Таганай/12_Разнарядки/Разнорядки 2025/Сводная_ведомость.xlsx
@@ -651,7 +651,7 @@
         </is>
       </c>
       <c r="I6" s="7" t="n">
-        <v>46158.33358836502</v>
+        <v>46158.37212276458</v>
       </c>
     </row>
     <row r="7" ht="15" customHeight="1">

--- a/Дело3а-78-2026Таганай/12_Разнарядки/Разнорядки 2025/Сводная_ведомость.xlsx
+++ b/Дело3а-78-2026Таганай/12_Разнарядки/Разнорядки 2025/Сводная_ведомость.xlsx
@@ -651,7 +651,7 @@
         </is>
       </c>
       <c r="I6" s="7" t="n">
-        <v>46158.37212276458</v>
+        <v>46158.37269141215</v>
       </c>
     </row>
     <row r="7" ht="15" customHeight="1">
